--- a/trades/todays_live_trades.xlsx
+++ b/trades/todays_live_trades.xlsx
@@ -7,17 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live Trades 2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live Trades 2026-10-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Live Trades 2026-10-30'!$A$1:$AA$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;Rs &quot;#,##0;[Red]-&quot;Rs &quot;#,##0;&quot;Rs &quot;0"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%;0.0%"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +31,40 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +72,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,17 +502,391 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="65" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No trades recorded for today</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pool / Setup</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Entry Spot</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Stop Spot</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Target Spot</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Pts</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Spot</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Time</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R-Multiple</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Expiry</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Entry Premium</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Premium</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Capital Deployed</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Value</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Est P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Lots</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.14R)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>22980.7</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>22950.1</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>23072.5</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>23053.45</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>78.67</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>114.32</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>20454</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>29723</v>
+      </c>
+      <c r="V2" s="7" t="n">
+        <v>9269</v>
+      </c>
+      <c r="W2" s="8" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.34R)</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>23006.25</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>22974.75</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>23100.75</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="T3" s="13" t="n">
+        <v>16190</v>
+      </c>
+      <c r="U3" s="13" t="n">
+        <v>25610</v>
+      </c>
+      <c r="V3" s="14" t="n">
+        <v>9420</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="X3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="9" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z3" s="10" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA3" s="10" t="inlineStr">
+        <is>
+          <t>paper</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>